--- a/config/data/ValueExpression.xlsx
+++ b/config/data/ValueExpression.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueExpression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ValueExpression" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2133"/>
+  <dimension ref="A1:J2134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -47233,6 +47233,26 @@
       <c r="E2133" t="inlineStr">
         <is>
           <t>{"type":"CheckedBinary","operator":"CheckedMultiply","left_expression_id":1031101,"right_expression_id":1031110,"rounding":"NearestTiesAway"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="B2134" t="n">
+        <v>24204</v>
+      </c>
+      <c r="C2134" t="inlineStr">
+        <is>
+          <t>program.clara.expr.counter-charges</t>
+        </is>
+      </c>
+      <c r="D2134" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E2134" t="inlineStr">
+        <is>
+          <t>{"type":"ReadStateSlot","state_slot_id":24206}</t>
         </is>
       </c>
     </row>

--- a/config/data/ValueExpression.xlsx
+++ b/config/data/ValueExpression.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2134"/>
+  <dimension ref="A1:J2147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -47253,6 +47253,266 @@
       <c r="E2134" t="inlineStr">
         <is>
           <t>{"type":"ReadStateSlot","state_slot_id":24206}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="B2135" t="n">
+        <v>970101</v>
+      </c>
+      <c r="C2135" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.resolved-base</t>
+        </is>
+      </c>
+      <c r="D2135" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2135" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"100.9"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="B2136" t="n">
+        <v>970102</v>
+      </c>
+      <c r="C2136" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.original</t>
+        </is>
+      </c>
+      <c r="D2136" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2136" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"0.8"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="B2137" t="n">
+        <v>970103</v>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.merrymaking</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"-0.5"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="B2138" t="n">
+        <v>970104</v>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.target-resistance</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2138" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"-0.2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="B2139" t="n">
+        <v>970105</v>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.penetration</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2139" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"0.1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="B2140" t="n">
+        <v>970106</v>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.resistance-minimum</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2140" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"-1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="B2141" t="n">
+        <v>970107</v>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.resistance-maximum</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2141" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"0.9"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="B2142" t="n">
+        <v>970108</v>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.unbroken</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2142" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"0.9"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="B2143" t="n">
+        <v>970109</v>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.one</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2143" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"1"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="B2144" t="n">
+        <v>970110</v>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.owner-property</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2144" t="inlineStr">
+        <is>
+          <t>{"type":"QueryStat","subject_selector_id":24051,"stat":"Elation","formula_purpose":"Stat"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="B2145" t="n">
+        <v>970111</v>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.resolved-meter</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2145" t="inlineStr">
+        <is>
+          <t>{"type":"CheckedBinary","operator":"CheckedAdd","left_expression_id":970109,"right_expression_id":970110,"rounding":"NearestTiesEven"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="B2146" t="n">
+        <v>970112</v>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.property-addition</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>Scalar</t>
+        </is>
+      </c>
+      <c r="E2146" t="inlineStr">
+        <is>
+          <t>{"type":"ScalarLiteral","value_decimal":"0.5"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="B2147" t="n">
+        <v>970113</v>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>policy.probe.elation.expr.non-scalar-negative</t>
+        </is>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>{"type":"IntegerLiteral","value":1}</t>
         </is>
       </c>
     </row>
